--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487518_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487518_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1801</v>
+        <v>2.2859</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0721</v>
+        <v>2.8839</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8921</v>
+        <v>-0.598</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1978</v>
@@ -610,13 +610,13 @@
         <v>3.5253</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4977</v>
+        <v>0.6036</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9534</v>
+        <v>0.7652</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4556</v>
+        <v>-0.1616</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6659</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7694</v>
+        <v>0.963</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5805</v>
+        <v>2.4157</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8112</v>
+        <v>-1.4527</v>
       </c>
       <c r="G3" t="n">
         <v>3.2788</v>
@@ -688,13 +688,13 @@
         <v>4.3087</v>
       </c>
       <c r="S3" t="n">
-        <v>0.274</v>
+        <v>0.4676</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5893</v>
+        <v>0.2458</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8633</v>
+        <v>0.2217</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2166</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LATAS CHICO</t>
+          <t>X. FOLCH CLARAMUNT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4239</v>
+        <v>0.2333</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1871</v>
+        <v>0.0838</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7632</v>
+        <v>0.1495</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.8226</v>
+        <v>-0.0946</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1148</v>
+        <v>-0.3675</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.7078</v>
+        <v>0.2729</v>
       </c>
       <c r="J4" t="n">
-        <v>1.269</v>
+        <v>0.0408</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1737</v>
+        <v>0.0408</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0953</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.0916</v>
+        <v>-0.1354</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2884</v>
+        <v>-0.4083</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.8031</v>
+        <v>0.2729</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.1128</v>
+        <v>0.1958</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2453</v>
+        <v>0.132</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7544</v>
+        <v>0.0429</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5091</v>
+        <v>0.0891</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1014</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>M. LATAS CHICO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1427</v>
+        <v>0.1425</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7237</v>
+        <v>0.6919</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.581</v>
+        <v>-0.5493</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9478</v>
+        <v>-2.8226</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1647</v>
+        <v>-0.1148</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7831</v>
+        <v>-2.7078</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1355</v>
+        <v>1.269</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1258</v>
+        <v>1.1737</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0953</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0833</v>
+        <v>-4.0916</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2905</v>
+        <v>-1.2884</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7927</v>
+        <v>-2.8031</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9377</v>
+        <v>4.1128</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0732</v>
+        <v>0.964</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2921</v>
+        <v>1.2592</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2189</v>
+        <v>-0.2952</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9412</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2754</v>
+        <v>1.1014</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. FOLCH CLARAMUNT</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0775</v>
+        <v>-0.3244</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0186</v>
+        <v>0.3337</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0961</v>
+        <v>-0.6581</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0946</v>
+        <v>-1.1785</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3675</v>
+        <v>-0.0065</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2729</v>
+        <v>-1.172</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0408</v>
+        <v>0.0319</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0408</v>
+        <v>0.6737</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6418</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1354</v>
+        <v>-1.2104</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4083</v>
+        <v>-0.6802</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2729</v>
+        <v>-0.5302</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0238</v>
+        <v>0.187</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0594</v>
+        <v>0.0265</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0356</v>
+        <v>0.1606</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5291</v>
+        <v>-0.5585</v>
       </c>
       <c r="E7" t="n">
-        <v>0.129</v>
+        <v>-0.1379</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6581</v>
+        <v>-0.4206</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1785</v>
+        <v>-1.9478</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0065</v>
+        <v>-1.1647</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.172</v>
+        <v>-0.7831</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0319</v>
+        <v>0.1355</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6737</v>
+        <v>0.1258</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6418</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2104</v>
+        <v>-2.0833</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6802</v>
+        <v>-1.2905</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5302</v>
+        <v>-0.7927</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3917</v>
+        <v>1.9585</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3917</v>
+        <v>2.9377</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0176</v>
+        <v>0.372</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1782</v>
+        <v>0.4305</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1606</v>
+        <v>-0.0585</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2754</v>
+        <v>-0.9412</v>
       </c>
       <c r="W7" t="n">
         <v>0.2754</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2936</v>
+        <v>-1.0087</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7398</v>
+        <v>-0.5351</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5538</v>
+        <v>-0.4736</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2283</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0653</v>
+        <v>0.2195</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>0.0859</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9685</v>
+        <v>-1.0532</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3301</v>
+        <v>0.505</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6384</v>
+        <v>-1.5582</v>
       </c>
       <c r="G9" t="n">
         <v>0.07580000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>3.3294</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5904</v>
+        <v>-0.675</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9922</v>
+        <v>-0.157</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5982</v>
+        <v>-0.518</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8249</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.183</v>
+        <v>-2.559</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9092</v>
+        <v>-1.6049</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0921</v>
+        <v>-0.9542</v>
       </c>
       <c r="G10" t="n">
-        <v>0.019</v>
+        <v>-2.6036</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0874</v>
+        <v>-1.0626</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1064</v>
+        <v>-1.541</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5251</v>
+        <v>-0.9162</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4083</v>
+        <v>-0.3148</v>
       </c>
       <c r="L10" t="n">
-        <v>3.1168</v>
+        <v>-0.6014</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5061</v>
+        <v>-1.6874</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4957</v>
+        <v>-0.7479</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0104</v>
+        <v>-0.9396</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3502</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3648</v>
+        <v>0.4362</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0257</v>
+        <v>0.2905</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3391</v>
+        <v>0.1457</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7813</v>
+        <v>-2.6444</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0142</v>
+        <v>0.6616</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.767</v>
+        <v>-3.306</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6036</v>
+        <v>0.019</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0626</v>
+        <v>-1.0874</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.541</v>
+        <v>1.1064</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9162</v>
+        <v>3.5251</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3148</v>
+        <v>0.4083</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6014</v>
+        <v>3.1168</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6874</v>
+        <v>-3.5061</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7479</v>
+        <v>-1.4957</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9396</v>
+        <v>-2.0104</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3917</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>0.214</v>
+        <v>0.9034</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1188</v>
+        <v>0.7781</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3328</v>
+        <v>0.1253</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9808</v>
+        <v>-4.3622</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7148</v>
+        <v>-2.2032</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2659</v>
+        <v>-2.159</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6988</v>
@@ -1390,13 +1390,13 @@
         <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4986</v>
+        <v>0.12</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.297</v>
+        <v>0.2147</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2016</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0076</v>
+        <v>-5.6705</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1881</v>
+        <v>-3.9045</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8195</v>
+        <v>-1.766</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1167</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0261</v>
+        <v>0.3632</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5891</v>
+        <v>0.8728</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5631</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.6083</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.1503</v>
+        <v>-14.5562</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.404000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-13.7462</v>
@@ -1522,7 +1522,7 @@
         <v>16.3955</v>
       </c>
       <c r="K14" t="n">
-        <v>9.832499999999998</v>
+        <v>9.8325</v>
       </c>
       <c r="L14" t="n">
         <v>6.5629</v>
@@ -1537,7 +1537,7 @@
         <v>-16.6666</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9794</v>
+        <v>-0.9794000000000009</v>
       </c>
       <c r="Q14" t="n">
         <v>-24.481</v>
@@ -1546,19 +1546,19 @@
         <v>23.5017</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4994</v>
+        <v>4.093500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>4.261</v>
+        <v>4.8551</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.7615000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-4.1554</v>
       </c>
       <c r="W14" t="n">
-        <v>2.420799999999999</v>
+        <v>2.4208</v>
       </c>
       <c r="X14" t="n">
         <v>-6.5763</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2203</v>
+        <v>5.9212</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0947</v>
+        <v>6.314</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1256</v>
+        <v>-0.3928</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1525</v>
+        <v>2.8042</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5856</v>
+        <v>1.9255</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5669</v>
+        <v>0.8788</v>
       </c>
       <c r="J15" t="n">
-        <v>5.891</v>
+        <v>4.3448</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4001</v>
+        <v>3.0775</v>
       </c>
       <c r="L15" t="n">
-        <v>4.4909</v>
+        <v>1.2673</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7385</v>
+        <v>-1.5406</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8145</v>
+        <v>-1.152</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.924</v>
+        <v>-0.3886</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5875</v>
+        <v>2.3502</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.546</v>
+        <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4803</v>
+        <v>-1.1157</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1622</v>
+        <v>-0.464</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6819</v>
+        <v>-0.6516</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.8825</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1616</v>
+        <v>5.1658</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9046</v>
+        <v>4.583</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.743</v>
+        <v>0.5829</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8042</v>
+        <v>4.1525</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9255</v>
+        <v>0.5856</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8788</v>
+        <v>3.5669</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3448</v>
+        <v>5.891</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0775</v>
+        <v>1.4001</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2673</v>
+        <v>4.4909</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5406</v>
+        <v>-1.7385</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.152</v>
+        <v>-0.8145</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3886</v>
+        <v>-0.924</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3502</v>
+        <v>0.5875</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3502</v>
+        <v>2.546</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8753</v>
+        <v>0.4258</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8734</v>
+        <v>0.6505</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0019</v>
+        <v>-0.2247</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8825</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4868</v>
+        <v>2.8834</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3645</v>
+        <v>3.1252</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1223</v>
+        <v>-0.2419</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0622</v>
+        <v>2.9456</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6608000000000001</v>
+        <v>-1.1616</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.723</v>
+        <v>4.1071</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6856</v>
+        <v>5.0174</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7472</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0615</v>
+        <v>5.0259</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7479</v>
+        <v>-2.0718</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0864</v>
+        <v>-1.153</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6615</v>
+        <v>-0.9188</v>
       </c>
       <c r="P17" t="n">
-        <v>2.546</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R17" t="n">
-        <v>2.546</v>
+        <v>3.7211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1122</v>
+        <v>0.1337</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3211</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.209</v>
+        <v>-0.3992</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1152</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1152</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.374</v>
+        <v>2.7579</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1531</v>
+        <v>1.8762</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.779</v>
+        <v>0.8818</v>
       </c>
       <c r="G18" t="n">
-        <v>2.404</v>
+        <v>-0.0622</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1259</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2781</v>
+        <v>-0.723</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8842</v>
+        <v>1.6856</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9394</v>
+        <v>1.7472</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9447</v>
+        <v>-0.0615</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4801</v>
+        <v>-1.7479</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8135</v>
+        <v>-1.0864</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6667</v>
+        <v>-0.6615</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9792</v>
+        <v>2.546</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9792</v>
+        <v>2.546</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6763</v>
+        <v>0.1589</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3982</v>
+        <v>0.1906</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2781</v>
+        <v>-0.0316</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3329</v>
+        <v>0.1152</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1243</v>
+        <v>2.2938</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.1531</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5643</v>
+        <v>-0.8592</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2322</v>
+        <v>2.404</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4502</v>
+        <v>1.1259</v>
       </c>
       <c r="I19" t="n">
-        <v>0.218</v>
+        <v>1.2781</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7554</v>
+        <v>3.8842</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4321</v>
+        <v>1.9394</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3233</v>
+        <v>1.9447</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9875</v>
+        <v>-1.4801</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8822</v>
+        <v>-0.8135</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1053</v>
+        <v>-0.6667</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3502</v>
+        <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7066</v>
+        <v>-0.7565</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2296</v>
+        <v>-0.3982</v>
       </c>
       <c r="U19" t="n">
-        <v>0.477</v>
+        <v>-0.3583</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="W19" t="n">
-        <v>1.492</v>
+        <v>-0.3329</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.014</v>
+        <v>1.3078</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7159</v>
+        <v>0.1972</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7019</v>
+        <v>1.1106</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9456</v>
+        <v>0.4316</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1616</v>
+        <v>0.1892</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1071</v>
+        <v>0.2425</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0174</v>
+        <v>2.3191</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.5463</v>
       </c>
       <c r="L20" t="n">
-        <v>5.0259</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0718</v>
+        <v>-1.8874</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.153</v>
+        <v>-1.3572</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9188</v>
+        <v>-0.5302</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
-        <v>3.7211</v>
+        <v>2.9377</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7357</v>
+        <v>0.6008</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1235</v>
+        <v>0.5405</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8592</v>
+        <v>0.0603</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W20" t="n">
-        <v>1.492</v>
+        <v>0.2754</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5613</v>
+        <v>1.2463</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5042</v>
+        <v>1.63</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0572</v>
+        <v>-0.3837</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4316</v>
+        <v>4.9011</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1892</v>
+        <v>2.0157</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2425</v>
+        <v>2.8854</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3191</v>
+        <v>6.0199</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5463</v>
+        <v>2.625</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7727000000000001</v>
+        <v>3.3949</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8874</v>
+        <v>-1.1188</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3572</v>
+        <v>-0.6093</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5302</v>
+        <v>-0.5095</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9377</v>
+        <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8542999999999999</v>
+        <v>-1.0085</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8475</v>
+        <v>-0.4729</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0068</v>
+        <v>-0.5356</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2754</v>
+        <v>-0.8837</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7954</v>
+        <v>0.4298</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4254</v>
+        <v>-0.8727</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6299</v>
+        <v>1.3026</v>
       </c>
       <c r="G22" t="n">
-        <v>4.9011</v>
+        <v>-0.2322</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0157</v>
+        <v>-0.4502</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8854</v>
+        <v>0.218</v>
       </c>
       <c r="J22" t="n">
-        <v>6.0199</v>
+        <v>0.7554</v>
       </c>
       <c r="K22" t="n">
-        <v>2.625</v>
+        <v>0.4321</v>
       </c>
       <c r="L22" t="n">
-        <v>3.3949</v>
+        <v>0.3233</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1188</v>
+        <v>-0.9875</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6093</v>
+        <v>-0.8822</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5095</v>
+        <v>-0.1053</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7626</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.917</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1543</v>
+        <v>2.3502</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4593</v>
+        <v>1.0122</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6775</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7818000000000001</v>
+        <v>0.2153</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8837</v>
+        <v>1.2166</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8837</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8188</v>
+        <v>-2.2952</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0855</v>
+        <v>-2.7785</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2667</v>
+        <v>0.4833</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7389</v>
@@ -2248,13 +2248,13 @@
         <v>2.9377</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2757</v>
+        <v>-0.7521</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7546</v>
+        <v>-0.4476</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5211</v>
+        <v>-0.3045</v>
       </c>
       <c r="V23" t="n">
         <v>1.2166</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7687</v>
+        <v>-3.1961</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8905</v>
+        <v>-3.4811</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1218</v>
+        <v>0.285</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0907</v>
@@ -2326,13 +2326,13 @@
         <v>1.9585</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4061</v>
+        <v>-0.8335</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5764</v>
+        <v>-0.167</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8297</v>
+        <v>-0.6665</v>
       </c>
       <c r="V24" t="n">
         <v>0.6659</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.1502</v>
+        <v>16.51469999999999</v>
       </c>
       <c r="E25" t="n">
         <v>13.7464</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4041</v>
+        <v>2.7686</v>
       </c>
       <c r="G25" t="n">
         <v>13.515</v>
       </c>
       <c r="H25" t="n">
-        <v>3.411199999999999</v>
+        <v>3.4112</v>
       </c>
       <c r="I25" t="n">
         <v>10.1038</v>
@@ -2392,10 +2392,10 @@
         <v>-9.832600000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.562999999999999</v>
+        <v>-6.563</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9791999999999996</v>
+        <v>0.9792000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-23.5019</v>
@@ -2404,13 +2404,13 @@
         <v>24.4809</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4994</v>
+        <v>-2.1349</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7615999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.2609</v>
+        <v>-2.8964</v>
       </c>
       <c r="V25" t="n">
         <v>4.1556</v>
